--- a/data/s4/Kanaleneiland/archetypes/pop_archetypes_citizen.xlsx
+++ b/data/s4/Kanaleneiland/archetypes/pop_archetypes_citizen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s4\Kanaleneiland\archetypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Kanaleneiland\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A01490-844D-484C-A22C-A95BC26F6316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6856223F-62AC-40F4-A262-0A110E50AA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,18 +205,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -231,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -239,7 +233,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,16 +636,16 @@
       <c r="AD1" t="s">
         <v>34</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AE1" t="s">
         <v>35</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AF1" t="s">
         <v>36</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AG1" t="s">
         <v>37</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AH1" t="s">
         <v>38</v>
       </c>
       <c r="AI1" s="2"/>
@@ -748,21 +741,17 @@
       <c r="AD2">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="AE2" s="7">
-        <f>12764*0.87</f>
-        <v>11104.68</v>
-      </c>
-      <c r="AF2" s="7">
-        <f>587*0.87</f>
-        <v>510.69</v>
-      </c>
-      <c r="AG2" s="7">
-        <f>14597*0.87</f>
-        <v>12699.39</v>
-      </c>
-      <c r="AH2" s="7">
-        <f>1459*0.87</f>
-        <v>1269.33</v>
+      <c r="AE2">
+        <v>12764</v>
+      </c>
+      <c r="AF2">
+        <v>587</v>
+      </c>
+      <c r="AG2">
+        <v>14597</v>
+      </c>
+      <c r="AH2">
+        <v>1459</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
@@ -856,21 +845,17 @@
       <c r="AD3">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="AE3" s="7">
-        <f>10415*0.87</f>
-        <v>9061.0499999999993</v>
-      </c>
-      <c r="AF3" s="7">
-        <f>636*0.87</f>
-        <v>553.32000000000005</v>
-      </c>
-      <c r="AG3" s="7">
-        <f>10736*0.87</f>
-        <v>9340.32</v>
-      </c>
-      <c r="AH3" s="7">
-        <f>1303*0.87</f>
-        <v>1133.6099999999999</v>
+      <c r="AE3">
+        <v>10415</v>
+      </c>
+      <c r="AF3">
+        <v>636</v>
+      </c>
+      <c r="AG3">
+        <v>10736</v>
+      </c>
+      <c r="AH3">
+        <v>1303</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.3">
@@ -964,21 +949,17 @@
       <c r="AD4">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="AE4" s="7">
-        <f>3822*0.87</f>
-        <v>3325.14</v>
-      </c>
-      <c r="AF4" s="7">
-        <f>402*0.87</f>
-        <v>349.74</v>
-      </c>
-      <c r="AG4" s="7">
-        <f>6860*0.87</f>
-        <v>5968.2</v>
-      </c>
-      <c r="AH4" s="7">
-        <f>1279*0.87</f>
-        <v>1112.73</v>
+      <c r="AE4">
+        <v>3822</v>
+      </c>
+      <c r="AF4">
+        <v>402</v>
+      </c>
+      <c r="AG4">
+        <v>6860</v>
+      </c>
+      <c r="AH4">
+        <v>1279</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
@@ -1072,21 +1053,17 @@
       <c r="AD5">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="AE5" s="7">
-        <f>5900*0.87</f>
-        <v>5133</v>
-      </c>
-      <c r="AF5" s="7">
-        <f>1259*0.87</f>
-        <v>1095.33</v>
-      </c>
-      <c r="AG5" s="7">
-        <f>10735*0.87</f>
-        <v>9339.4500000000007</v>
-      </c>
-      <c r="AH5" s="7">
-        <f>1698*0.87</f>
-        <v>1477.26</v>
+      <c r="AE5">
+        <v>5900</v>
+      </c>
+      <c r="AF5">
+        <v>1259</v>
+      </c>
+      <c r="AG5">
+        <v>10735</v>
+      </c>
+      <c r="AH5">
+        <v>1698</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.3">
@@ -1180,21 +1157,17 @@
       <c r="AD6">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="AE6" s="7">
-        <f>12301*0.87</f>
-        <v>10701.87</v>
-      </c>
-      <c r="AF6" s="7">
-        <f>1298*0.87</f>
-        <v>1129.26</v>
-      </c>
-      <c r="AG6" s="7">
-        <f>13621*0.87</f>
-        <v>11850.27</v>
-      </c>
-      <c r="AH6" s="7">
-        <f>1933*0.87</f>
-        <v>1681.71</v>
+      <c r="AE6">
+        <v>12301</v>
+      </c>
+      <c r="AF6">
+        <v>1298</v>
+      </c>
+      <c r="AG6">
+        <v>13621</v>
+      </c>
+      <c r="AH6">
+        <v>1933</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.3">
